--- a/Hyderabad-February-2026.xlsx
+++ b/Hyderabad-February-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="72">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Hyderabad</t>
   </si>
   <si>
@@ -148,13 +151,13 @@
     <t>MH43BP4027</t>
   </si>
   <si>
-    <t>TS09UE 3183</t>
-  </si>
-  <si>
-    <t>TS09UE 3184</t>
-  </si>
-  <si>
-    <t>TS09UE 3198</t>
+    <t>TS09UE3183</t>
+  </si>
+  <si>
+    <t>TS09UE3184</t>
+  </si>
+  <si>
+    <t>TS09UE3198</t>
   </si>
   <si>
     <t>TS09UE3947</t>
@@ -175,25 +178,25 @@
     <t>JAGUAR</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Etios</t>
-  </si>
-  <si>
-    <t>Bolero</t>
-  </si>
-  <si>
-    <t>Safari</t>
-  </si>
-  <si>
-    <t>BYD</t>
-  </si>
-  <si>
-    <t>Dzire</t>
+    <t>ETIOS</t>
+  </si>
+  <si>
+    <t>BOLERO</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>BYD E6</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>29/09/2018</t>
@@ -223,10 +226,10 @@
     <t>17/07/2019</t>
   </si>
   <si>
+    <t>14/03/2024</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>14/03/2024</t>
   </si>
 </sst>
 </file>
@@ -588,10 +591,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,28 +673,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H2">
         <v>133659</v>
@@ -751,27 +757,27 @@
         <v>77.83</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>98</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H3">
         <v>179180</v>
@@ -831,27 +837,27 @@
         <v>65.59999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4">
         <v>133384</v>
@@ -911,24 +917,24 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" s="2">
         <v>44572</v>
@@ -991,24 +997,24 @@
         <v>46.17</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2">
         <v>44572</v>
@@ -1071,27 +1077,27 @@
         <v>61.35</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>102</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2026</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>134242</v>
@@ -1151,27 +1157,27 @@
         <v>29.84</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>103</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H8">
         <v>110907</v>
@@ -1231,27 +1237,27 @@
         <v>35.65</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>104</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2026</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H9">
         <v>65792</v>
@@ -1311,24 +1317,24 @@
         <v>73.08</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>105</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2">
         <v>45235</v>
@@ -1391,27 +1397,27 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>106</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2026</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H11">
         <v>66100</v>
@@ -1471,24 +1477,24 @@
         <v>60.39</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>107</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2026</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12" s="2">
         <v>44628</v>
@@ -1551,24 +1557,24 @@
         <v>54.76</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2026</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2">
         <v>45570</v>
@@ -1631,24 +1637,24 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>109</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2026</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" s="2">
         <v>44629</v>
@@ -1711,27 +1717,27 @@
         <v>54.55</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>110</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H15">
         <v>82150</v>
@@ -1791,27 +1797,27 @@
         <v>40.58</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>111</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2026</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16">
         <v>117163</v>
@@ -1876,22 +1882,22 @@
         <v>112</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2026</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17">
         <v>76347</v>
@@ -1956,22 +1962,22 @@
         <v>113</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2026</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" t="s">
-        <v>69</v>
+        <v>57</v>
+      </c>
+      <c r="G18" s="2">
+        <v>45352</v>
       </c>
       <c r="H18">
         <v>137338</v>
@@ -2036,22 +2042,22 @@
         <v>114</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2026</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" t="s">
-        <v>69</v>
+        <v>57</v>
+      </c>
+      <c r="G19" s="2">
+        <v>45352</v>
       </c>
       <c r="H19">
         <v>133187</v>
@@ -2108,7 +2114,7 @@
         <v>-31238</v>
       </c>
       <c r="Z19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:26">
@@ -2116,22 +2122,22 @@
         <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2026</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" t="s">
-        <v>69</v>
+        <v>57</v>
+      </c>
+      <c r="G20" s="2">
+        <v>45352</v>
       </c>
       <c r="H20">
         <v>131501</v>
@@ -2196,19 +2202,19 @@
         <v>116</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2026</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" s="2">
         <v>45629</v>
@@ -2276,19 +2282,19 @@
         <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2026</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G22" s="2">
         <v>45629</v>
@@ -2356,19 +2362,19 @@
         <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2026</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" t="s">
         <v>70</v>
@@ -2436,19 +2442,19 @@
         <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2026</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2">
         <v>45569</v>
@@ -2516,19 +2522,19 @@
         <v>120</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2026</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G25" s="2">
         <v>45569</v>
